--- a/StructureDefinition-chul-encounter.xlsx
+++ b/StructureDefinition-chul-encounter.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$97</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3814" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3491" uniqueCount="509">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T14:51:56+02:00</t>
+    <t>2025-09-10T16:13:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -515,32 +515,68 @@
     <t>Identifier(s) by which this encounter is known.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:system}
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>PV1-19</t>
+  </si>
+  <si>
+    <t>Encounter.status</t>
+  </si>
+  <si>
+    <t>Status of this Hospital stay</t>
+  </si>
+  <si>
+    <t>At the discharge report status of the encounter should be always = "finished"</t>
+  </si>
+  <si>
+    <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.eu/fhir/hdr/ValueSet/encounter-status-eu-hdr</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>No clear equivalent in HL7 v2; active/finished could be inferred from PV1-44, PV1-45, PV2-24; inactive could be inferred from PV2-16</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
 </t>
   </si>
   <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>PV1-19</t>
-  </si>
-  <si>
-    <t>Encounter.identifier:chulIdentifier</t>
-  </si>
-  <si>
-    <t>chulIdentifier</t>
-  </si>
-  <si>
-    <t>Encounter.identifier:chulIdentifier.id</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.id</t>
+    <t>List of past encounter statuses</t>
+  </si>
+  <si>
+    <t>The status history permits the encounter resource to contain the status history without needing to read through the historical versions of the resource, or even have the server store them.</t>
+  </si>
+  <si>
+    <t>The current status is always found in the current version of the resource, not the status history.</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -556,13 +592,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Encounter.identifier:chulIdentifier.extension</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.extension</t>
+    <t>Encounter.statusHistory.extension</t>
   </si>
   <si>
     <t>Additional content defined by implementations</t>
@@ -571,356 +601,129 @@
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Encounter.identifier:chulIdentifier.use</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Encounter.identifier:chulIdentifier.type</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.type</t>
+    <t>Encounter.statusHistory.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.status</t>
+  </si>
+  <si>
+    <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +</t>
+  </si>
+  <si>
+    <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +.</t>
+  </si>
+  <si>
+    <t>Current state of the encounter.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>The time that the episode was in the specified status</t>
+  </si>
+  <si>
+    <t>The time that the episode was in the specified status.</t>
+  </si>
+  <si>
+    <t>Encounter.class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Classification of patient encounter</t>
+  </si>
+  <si>
+    <t>Concepts representing classification of inpatient encounter such as inpatient, emergency or others due to local variations.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.eu/fhir/hdr/ValueSet/hdr-encounterClass-eu-hdr</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>PV1-2</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory</t>
+  </si>
+  <si>
+    <t>List of past encounter classes</t>
+  </si>
+  <si>
+    <t>The class history permits the tracking of the encounters transitions without needing to go  through the resource history.  This would be used for a case where an admission starts of as an emergency encounter, then transitions into an inpatient scenario. Doing this and not restarting a new encounter ensures that any lab/diagnostic results can more easily follow the patient and not require re-processing and not get lost or cancelled during a kind of discharge from emergency to inpatient.</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.id</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.extension</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.class</t>
+  </si>
+  <si>
+    <t>inpatient | outpatient | ambulatory | emergency +</t>
+  </si>
+  <si>
+    <t>inpatient | outpatient | ambulatory | emergency +.</t>
+  </si>
+  <si>
+    <t>Classification of the encounter.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
+  </si>
+  <si>
+    <t>Encounter.classHistory.period</t>
+  </si>
+  <si>
+    <t>The time that the episode was in the specified class</t>
+  </si>
+  <si>
+    <t>The time that the episode was in the specified class.</t>
+  </si>
+  <si>
+    <t>Encounter.type</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Encounter.identifier:chulIdentifier.system</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>https://terminology.chuliege.be/NamingSystem/location</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>Encounter.identifier:chulIdentifier.value</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>http://si-s-serv1041.st.chulg/ig/VersUnSouffleNouveauIG/ValueSet/chul-location</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>Encounter.identifier:chulIdentifier.period</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Encounter.identifier:chulIdentifier.assigner</t>
-  </si>
-  <si>
-    <t>Encounter.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>Encounter.status</t>
-  </si>
-  <si>
-    <t>Status of this Hospital stay</t>
-  </si>
-  <si>
-    <t>At the discharge report status of the encounter should be always = "finished"</t>
-  </si>
-  <si>
-    <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
-  </si>
-  <si>
-    <t>http://hl7.eu/fhir/hdr/ValueSet/encounter-status-eu-hdr</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>No clear equivalent in HL7 v2; active/finished could be inferred from PV1-44, PV1-45, PV2-24; inactive could be inferred from PV2-16</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>List of past encounter statuses</t>
-  </si>
-  <si>
-    <t>The status history permits the encounter resource to contain the status history without needing to read through the historical versions of the resource, or even have the server store them.</t>
-  </si>
-  <si>
-    <t>The current status is always found in the current version of the resource, not the status history.</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.id</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.extension</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.status</t>
-  </si>
-  <si>
-    <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +</t>
-  </si>
-  <si>
-    <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +.</t>
-  </si>
-  <si>
-    <t>Current state of the encounter.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.period</t>
-  </si>
-  <si>
-    <t>The time that the episode was in the specified status</t>
-  </si>
-  <si>
-    <t>The time that the episode was in the specified status.</t>
-  </si>
-  <si>
-    <t>Encounter.class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Classification of patient encounter</t>
-  </si>
-  <si>
-    <t>Concepts representing classification of inpatient encounter such as inpatient, emergency or others due to local variations.</t>
-  </si>
-  <si>
-    <t>http://hl7.eu/fhir/hdr/ValueSet/hdr-encounterClass-eu-hdr</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>PV1-2</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory</t>
-  </si>
-  <si>
-    <t>List of past encounter classes</t>
-  </si>
-  <si>
-    <t>The class history permits the tracking of the encounters transitions without needing to go  through the resource history.  This would be used for a case where an admission starts of as an emergency encounter, then transitions into an inpatient scenario. Doing this and not restarting a new encounter ensures that any lab/diagnostic results can more easily follow the patient and not require re-processing and not get lost or cancelled during a kind of discharge from emergency to inpatient.</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.id</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.extension</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.class</t>
-  </si>
-  <si>
-    <t>inpatient | outpatient | ambulatory | emergency +</t>
-  </si>
-  <si>
-    <t>inpatient | outpatient | ambulatory | emergency +.</t>
-  </si>
-  <si>
-    <t>Classification of the encounter.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
-  </si>
-  <si>
-    <t>Encounter.classHistory.period</t>
-  </si>
-  <si>
-    <t>The time that the episode was in the specified class</t>
-  </si>
-  <si>
-    <t>The time that the episode was in the specified class.</t>
-  </si>
-  <si>
-    <t>Encounter.type</t>
   </si>
   <si>
     <t>Specific type of Hospital stay</t>
@@ -2121,12 +1924,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN106"/>
+  <dimension ref="A1:AN97"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.359375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.98828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.0234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="11.1328125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
@@ -2143,16 +1946,16 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.8125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.56640625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.6015625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="72.99609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.1875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.8203125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="44.98828125" customWidth="true" bestFit="true" hidden="true"/>
@@ -2160,7 +1963,7 @@
     <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="99.69140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="89.546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="184.87890625" customWidth="true" bestFit="true"/>
   </cols>
@@ -3550,7 +3353,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>78</v>
@@ -3610,14 +3413,16 @@
         <v>19</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AC13" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD13" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>156</v>
@@ -3635,28 +3440,26 @@
         <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>163</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>19</v>
       </c>
@@ -3671,21 +3474,23 @@
         <v>19</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>19</v>
@@ -3710,13 +3515,11 @@
         <v>19</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>19</v>
@@ -3734,13 +3537,13 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>19</v>
@@ -3749,24 +3552,24 @@
         <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>163</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3777,7 +3580,7 @@
         <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>19</v>
@@ -3789,15 +3592,17 @@
         <v>19</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>19</v>
@@ -3846,25 +3651,25 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>19</v>
@@ -3875,21 +3680,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>19</v>
@@ -3901,17 +3706,15 @@
         <v>19</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>19</v>
@@ -3948,37 +3751,37 @@
         <v>19</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>19</v>
@@ -3989,46 +3792,44 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>19</v>
       </c>
@@ -4052,98 +3853,98 @@
         <v>19</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c r="Z17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>188</v>
-      </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>129</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>192</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>19</v>
@@ -4168,13 +3969,13 @@
         <v>19</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>197</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>198</v>
+        <v>19</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>199</v>
+        <v>19</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>19</v>
@@ -4192,39 +3993,39 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>201</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4244,23 +4045,19 @@
         <v>19</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>19</v>
       </c>
@@ -4269,10 +4066,10 @@
         <v>19</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>209</v>
+        <v>19</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>19</v>
@@ -4284,13 +4081,13 @@
         <v>19</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>19</v>
+        <v>196</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>19</v>
+        <v>197</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>19</v>
@@ -4308,10 +4105,10 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>86</v>
@@ -4326,21 +4123,21 @@
         <v>19</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>212</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4348,7 +4145,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>86</v>
@@ -4360,20 +4157,18 @@
         <v>19</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>19</v>
@@ -4386,7 +4181,7 @@
         <v>19</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>218</v>
+        <v>19</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>19</v>
@@ -4398,11 +4193,13 @@
         <v>19</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y20" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z20" t="s" s="2">
-        <v>219</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>19</v>
@@ -4420,10 +4217,10 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>86</v>
@@ -4438,21 +4235,21 @@
         <v>19</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>221</v>
+        <v>178</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>222</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4460,7 +4257,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>86</v>
@@ -4475,13 +4272,13 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4508,13 +4305,11 @@
         <v>19</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>19</v>
+        <v>207</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>19</v>
@@ -4532,10 +4327,10 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>86</v>
@@ -4550,21 +4345,21 @@
         <v>19</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>230</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4575,7 +4370,7 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>19</v>
@@ -4584,20 +4379,18 @@
         <v>19</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>19</v>
@@ -4646,13 +4439,13 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>19</v>
@@ -4664,21 +4457,21 @@
         <v>19</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>239</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4686,7 +4479,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>86</v>
@@ -4695,23 +4488,21 @@
         <v>19</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>180</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>241</v>
+        <v>181</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>19</v>
@@ -4736,11 +4527,13 @@
         <v>19</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>244</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>19</v>
@@ -4758,10 +4551,10 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>183</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>86</v>
@@ -4770,31 +4563,31 @@
         <v>19</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>245</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>246</v>
+        <v>178</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>247</v>
+        <v>19</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>248</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4813,16 +4606,16 @@
         <v>19</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>185</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>252</v>
+        <v>186</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4872,7 +4665,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>249</v>
+        <v>187</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4884,13 +4677,13 @@
         <v>19</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>19</v>
@@ -4901,42 +4694,46 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>216</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>19</v>
       </c>
@@ -4984,25 +4781,25 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>19</v>
@@ -5013,21 +4810,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>217</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>217</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>19</v>
@@ -5039,17 +4836,15 @@
         <v>19</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>19</v>
@@ -5074,13 +4869,13 @@
         <v>19</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>19</v>
+        <v>220</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>19</v>
+        <v>221</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>19</v>
@@ -5098,25 +4893,25 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>19</v>
@@ -5127,46 +4922,42 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>19</v>
       </c>
@@ -5214,25 +5005,25 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>19</v>
@@ -5243,10 +5034,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5254,10 +5045,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>19</v>
@@ -5266,18 +5057,20 @@
         <v>19</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>262</v>
+        <v>227</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -5302,13 +5095,11 @@
         <v>19</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>264</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>265</v>
+        <v>231</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>19</v>
@@ -5326,13 +5117,13 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>19</v>
@@ -5341,24 +5132,24 @@
         <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>19</v>
+        <v>232</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>172</v>
+        <v>233</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>19</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5366,7 +5157,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>86</v>
@@ -5378,16 +5169,16 @@
         <v>19</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>267</v>
+        <v>236</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5414,13 +5205,13 @@
         <v>19</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>19</v>
+        <v>238</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>19</v>
+        <v>239</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>19</v>
@@ -5438,10 +5229,10 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>86</v>
@@ -5453,24 +5244,24 @@
         <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>19</v>
+        <v>232</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>19</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5478,7 +5269,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>86</v>
@@ -5490,16 +5281,16 @@
         <v>19</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5526,11 +5317,11 @@
         <v>19</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>19</v>
@@ -5548,10 +5339,10 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>86</v>
@@ -5566,32 +5357,32 @@
         <v>19</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>276</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>19</v>
@@ -5600,18 +5391,20 @@
         <v>19</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>250</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -5660,13 +5453,13 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>19</v>
@@ -5675,24 +5468,24 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>19</v>
+        <v>254</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>172</v>
+        <v>255</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>19</v>
+        <v>256</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>19</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5703,7 +5496,7 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>19</v>
@@ -5712,16 +5505,16 @@
         <v>19</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>168</v>
+        <v>259</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>169</v>
+        <v>260</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>170</v>
+        <v>261</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5772,43 +5565,43 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>171</v>
+        <v>258</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>19</v>
+        <v>262</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>19</v>
+        <v>263</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>19</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>150</v>
+        <v>266</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5827,17 +5620,15 @@
         <v>19</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>131</v>
+        <v>267</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>175</v>
+        <v>268</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>19</v>
@@ -5886,7 +5677,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>178</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5898,13 +5689,13 @@
         <v>19</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>19</v>
+        <v>270</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>172</v>
+        <v>271</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>19</v>
@@ -5915,14 +5706,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5935,26 +5726,22 @@
         <v>19</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>19</v>
       </c>
@@ -5990,19 +5777,17 @@
         <v>19</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -6014,27 +5799,27 @@
         <v>19</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>19</v>
+        <v>276</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>129</v>
+        <v>277</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>19</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6042,7 +5827,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>86</v>
@@ -6057,13 +5842,13 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>181</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>182</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6090,13 +5875,13 @@
         <v>19</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>197</v>
+        <v>19</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>286</v>
+        <v>19</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>19</v>
@@ -6114,10 +5899,10 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>183</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>86</v>
@@ -6126,13 +5911,13 @@
         <v>19</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>19</v>
@@ -6143,21 +5928,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>19</v>
@@ -6169,15 +5954,17 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>225</v>
+        <v>131</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>289</v>
+        <v>185</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6226,25 +6013,25 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>288</v>
+        <v>187</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>19</v>
@@ -6255,14 +6042,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6275,24 +6062,26 @@
         <v>19</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>292</v>
+        <v>190</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>293</v>
+        <v>191</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>19</v>
       </c>
@@ -6316,11 +6105,13 @@
         <v>19</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="Y37" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z37" t="s" s="2">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>19</v>
@@ -6338,7 +6129,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>291</v>
+        <v>192</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6350,27 +6141,27 @@
         <v>19</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>297</v>
+        <v>19</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>298</v>
+        <v>129</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>275</v>
+        <v>19</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>299</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6381,7 +6172,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>19</v>
@@ -6393,15 +6184,17 @@
         <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>19</v>
@@ -6426,13 +6219,13 @@
         <v>19</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>295</v>
+        <v>206</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>19</v>
@@ -6450,13 +6243,13 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>19</v>
@@ -6465,24 +6258,24 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>172</v>
+        <v>288</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>305</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6505,13 +6298,13 @@
         <v>19</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6538,11 +6331,13 @@
         <v>19</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>309</v>
+        <v>19</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>19</v>
@@ -6560,7 +6355,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6578,29 +6373,29 @@
         <v>19</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>311</v>
+        <v>19</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>312</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>314</v>
+        <v>19</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>86</v>
@@ -6615,17 +6410,15 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>19</v>
@@ -6674,7 +6467,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6689,26 +6482,28 @@
         <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>322</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>19</v>
       </c>
@@ -6729,13 +6524,13 @@
         <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>324</v>
+        <v>174</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6786,7 +6581,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6801,35 +6596,35 @@
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>327</v>
+        <v>276</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>172</v>
+        <v>277</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>328</v>
+        <v>19</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>329</v>
+        <v>278</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>330</v>
+        <v>279</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>331</v>
+        <v>19</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>19</v>
@@ -6841,13 +6636,13 @@
         <v>19</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>332</v>
+        <v>180</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>333</v>
+        <v>181</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>334</v>
+        <v>182</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6898,25 +6693,25 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>330</v>
+        <v>183</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>335</v>
+        <v>19</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>336</v>
+        <v>178</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>19</v>
@@ -6927,14 +6722,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>337</v>
+        <v>280</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6950,18 +6745,20 @@
         <v>19</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>338</v>
+        <v>185</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -6998,17 +6795,19 @@
         <v>19</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>337</v>
+        <v>187</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -7020,59 +6819,63 @@
         <v>19</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>341</v>
+        <v>19</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>342</v>
+        <v>178</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>343</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>281</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>19</v>
       </c>
@@ -7120,25 +6923,25 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>19</v>
@@ -7149,18 +6952,18 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>345</v>
+        <v>282</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>78</v>
@@ -7172,19 +6975,19 @@
         <v>19</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>131</v>
+        <v>226</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>175</v>
+        <v>283</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>153</v>
+        <v>285</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7195,7 +6998,7 @@
         <v>19</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>19</v>
+        <v>311</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>19</v>
@@ -7210,13 +7013,13 @@
         <v>19</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>19</v>
+        <v>284</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>19</v>
+        <v>286</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>19</v>
@@ -7234,7 +7037,7 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>178</v>
+        <v>282</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7246,63 +7049,59 @@
         <v>19</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>19</v>
+        <v>287</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>172</v>
+        <v>288</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>19</v>
+        <v>289</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>312</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>346</v>
+        <v>290</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>19</v>
       </c>
@@ -7350,39 +7149,39 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>129</v>
+        <v>293</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>19</v>
+        <v>294</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>347</v>
+        <v>313</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7393,7 +7192,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>19</v>
@@ -7405,17 +7204,15 @@
         <v>87</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>192</v>
+        <v>296</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -7440,13 +7237,13 @@
         <v>19</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>197</v>
+        <v>19</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>349</v>
+        <v>19</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>351</v>
+        <v>19</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>19</v>
@@ -7464,13 +7261,13 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>19</v>
@@ -7479,26 +7276,28 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>352</v>
+        <v>299</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>353</v>
+        <v>300</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>19</v>
+        <v>301</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>354</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>19</v>
       </c>
@@ -7507,7 +7306,7 @@
         <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>19</v>
@@ -7516,16 +7315,16 @@
         <v>19</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>356</v>
+        <v>316</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>357</v>
+        <v>306</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7576,13 +7375,13 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>355</v>
+        <v>272</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>19</v>
@@ -7591,24 +7390,24 @@
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>19</v>
+        <v>276</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>359</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>360</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>360</v>
+        <v>279</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7628,16 +7427,16 @@
         <v>19</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>361</v>
+        <v>180</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>362</v>
+        <v>181</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>363</v>
+        <v>182</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7688,7 +7487,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>360</v>
+        <v>183</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7700,33 +7499,31 @@
         <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>365</v>
+        <v>178</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>366</v>
+        <v>19</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>367</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>368</v>
+        <v>318</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7742,18 +7539,20 @@
         <v>19</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>370</v>
+        <v>185</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -7802,7 +7601,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>337</v>
+        <v>187</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7814,59 +7613,63 @@
         <v>19</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>341</v>
+        <v>19</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>342</v>
+        <v>178</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>343</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>319</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>344</v>
+        <v>281</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
       </c>
@@ -7914,25 +7717,25 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>19</v>
@@ -7943,18 +7746,18 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>345</v>
+        <v>282</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>78</v>
@@ -7966,19 +7769,19 @@
         <v>19</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>131</v>
+        <v>226</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>175</v>
+        <v>283</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>153</v>
+        <v>285</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7989,7 +7792,7 @@
         <v>19</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>19</v>
+        <v>321</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>19</v>
@@ -8004,13 +7807,13 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>19</v>
+        <v>284</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>19</v>
+        <v>286</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -8028,7 +7831,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>178</v>
+        <v>282</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -8040,63 +7843,59 @@
         <v>19</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>19</v>
+        <v>287</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>172</v>
+        <v>288</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>19</v>
+        <v>289</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>346</v>
+        <v>290</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>19</v>
       </c>
@@ -8144,39 +7943,39 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>129</v>
+        <v>293</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>19</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8184,10 +7983,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G54" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>19</v>
@@ -8199,17 +7998,15 @@
         <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>192</v>
+        <v>296</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -8219,7 +8016,7 @@
         <v>19</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>376</v>
+        <v>19</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>19</v>
@@ -8234,13 +8031,13 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>197</v>
+        <v>19</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>349</v>
+        <v>19</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>351</v>
+        <v>19</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>19</v>
@@ -8258,13 +8055,13 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>19</v>
@@ -8273,26 +8070,28 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>352</v>
+        <v>299</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>353</v>
+        <v>300</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>19</v>
+        <v>301</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>354</v>
+        <v>302</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>377</v>
+        <v>324</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>19</v>
       </c>
@@ -8301,7 +8100,7 @@
         <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>19</v>
@@ -8310,16 +8109,16 @@
         <v>19</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>357</v>
+        <v>306</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8370,13 +8169,13 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>355</v>
+        <v>272</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>19</v>
@@ -8385,24 +8184,24 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>19</v>
+        <v>276</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>359</v>
+        <v>278</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>378</v>
+        <v>327</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>360</v>
+        <v>279</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8422,16 +8221,16 @@
         <v>19</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>361</v>
+        <v>180</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>362</v>
+        <v>181</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>363</v>
+        <v>182</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8482,7 +8281,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>360</v>
+        <v>183</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8494,33 +8293,31 @@
         <v>19</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>365</v>
+        <v>178</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>366</v>
+        <v>19</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>367</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8536,18 +8333,20 @@
         <v>19</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>381</v>
+        <v>185</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>19</v>
@@ -8596,7 +8395,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>337</v>
+        <v>187</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8608,59 +8407,63 @@
         <v>19</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>341</v>
+        <v>19</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>342</v>
+        <v>178</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>343</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>382</v>
+        <v>329</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>344</v>
+        <v>281</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>19</v>
       </c>
@@ -8708,25 +8511,25 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>19</v>
@@ -8737,18 +8540,18 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>383</v>
+        <v>330</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>345</v>
+        <v>282</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>78</v>
@@ -8760,19 +8563,19 @@
         <v>19</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>131</v>
+        <v>226</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>175</v>
+        <v>283</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>153</v>
+        <v>285</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8783,7 +8586,7 @@
         <v>19</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>19</v>
+        <v>331</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>19</v>
@@ -8798,13 +8601,13 @@
         <v>19</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>19</v>
+        <v>206</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>19</v>
+        <v>284</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>19</v>
+        <v>286</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>19</v>
@@ -8822,7 +8625,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>178</v>
+        <v>282</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8834,63 +8637,59 @@
         <v>19</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>19</v>
+        <v>287</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>172</v>
+        <v>288</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>19</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>384</v>
+        <v>332</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>346</v>
+        <v>290</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>19</v>
       </c>
@@ -8938,39 +8737,39 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>129</v>
+        <v>293</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>19</v>
+        <v>294</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>385</v>
+        <v>333</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8978,10 +8777,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G61" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>19</v>
@@ -8993,17 +8792,15 @@
         <v>87</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>192</v>
+        <v>296</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>19</v>
@@ -9013,7 +8810,7 @@
         <v>19</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>386</v>
+        <v>19</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>19</v>
@@ -9028,13 +8825,13 @@
         <v>19</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>197</v>
+        <v>19</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>349</v>
+        <v>19</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>351</v>
+        <v>19</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>19</v>
@@ -9052,13 +8849,13 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>19</v>
@@ -9067,24 +8864,24 @@
         <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>352</v>
+        <v>299</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>353</v>
+        <v>300</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>19</v>
+        <v>301</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>354</v>
+        <v>302</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>387</v>
+        <v>334</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9095,7 +8892,7 @@
         <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>19</v>
@@ -9104,16 +8901,16 @@
         <v>19</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>225</v>
+        <v>335</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9164,13 +8961,13 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>19</v>
@@ -9179,24 +8976,24 @@
         <v>98</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>19</v>
+        <v>270</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>359</v>
+        <v>339</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>388</v>
+        <v>340</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9216,18 +9013,20 @@
         <v>19</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>361</v>
+        <v>199</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>19</v>
@@ -9276,7 +9075,7 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9291,28 +9090,26 @@
         <v>98</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>367</v>
+        <v>347</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>19</v>
       </c>
@@ -9321,7 +9118,7 @@
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>19</v>
@@ -9330,18 +9127,20 @@
         <v>19</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>250</v>
+        <v>349</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>391</v>
+        <v>350</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>19</v>
@@ -9390,13 +9189,13 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>19</v>
@@ -9405,35 +9204,35 @@
         <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>343</v>
+        <v>354</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>392</v>
+        <v>355</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>19</v>
+        <v>356</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>19</v>
@@ -9442,18 +9241,20 @@
         <v>19</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>168</v>
+        <v>226</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>169</v>
+        <v>357</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>19</v>
@@ -9478,13 +9279,11 @@
         <v>19</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>19</v>
@@ -9502,43 +9301,43 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>171</v>
+        <v>355</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>172</v>
+        <v>362</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>19</v>
+        <v>363</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>19</v>
+        <v>364</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>150</v>
+        <v>356</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9554,19 +9353,19 @@
         <v>19</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>131</v>
+        <v>366</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>175</v>
+        <v>367</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>176</v>
+        <v>358</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>153</v>
+        <v>359</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9616,7 +9415,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>178</v>
+        <v>365</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9628,31 +9427,31 @@
         <v>19</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>19</v>
+        <v>361</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>172</v>
+        <v>362</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>19</v>
+        <v>363</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>19</v>
+        <v>364</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9665,26 +9464,24 @@
         <v>19</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>258</v>
+        <v>369</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>259</v>
+        <v>370</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>19</v>
       </c>
@@ -9732,7 +9529,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>260</v>
+        <v>368</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9744,13 +9541,13 @@
         <v>19</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>129</v>
+        <v>372</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>19</v>
@@ -9761,10 +9558,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9772,11 +9569,11 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G68" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G68" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="H68" t="s" s="2">
         <v>19</v>
       </c>
@@ -9784,20 +9581,18 @@
         <v>19</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>348</v>
+        <v>181</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -9807,7 +9602,7 @@
         <v>19</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>396</v>
+        <v>19</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>19</v>
@@ -9822,13 +9617,13 @@
         <v>19</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>197</v>
+        <v>19</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>349</v>
+        <v>19</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>351</v>
+        <v>19</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>19</v>
@@ -9846,50 +9641,50 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>347</v>
+        <v>183</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>352</v>
+        <v>19</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>353</v>
+        <v>178</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>354</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>397</v>
+        <v>374</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>19</v>
@@ -9901,15 +9696,17 @@
         <v>19</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>225</v>
+        <v>131</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>356</v>
+        <v>185</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>19</v>
@@ -9958,71 +9755,75 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>355</v>
+        <v>187</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>358</v>
+        <v>178</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>359</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>361</v>
+        <v>131</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>362</v>
+        <v>190</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>19</v>
       </c>
@@ -10070,50 +9871,50 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>360</v>
+        <v>192</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>364</v>
+        <v>19</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>365</v>
+        <v>129</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>366</v>
+        <v>19</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>367</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>19</v>
+        <v>377</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>19</v>
@@ -10125,15 +9926,17 @@
         <v>87</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>400</v>
+        <v>378</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -10182,13 +9985,13 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>19</v>
@@ -10197,24 +10000,24 @@
         <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>335</v>
+        <v>381</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>19</v>
+        <v>363</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>404</v>
+        <v>383</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10237,17 +10040,15 @@
         <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -10272,13 +10073,13 @@
         <v>19</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>19</v>
+        <v>387</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>19</v>
+        <v>388</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>19</v>
@@ -10296,7 +10097,7 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10311,24 +10112,24 @@
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>409</v>
+        <v>19</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>410</v>
+        <v>178</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>411</v>
+        <v>19</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>412</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10351,17 +10152,15 @@
         <v>19</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>19</v>
@@ -10410,7 +10209,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10425,28 +10224,28 @@
         <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>409</v>
+        <v>19</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>419</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>421</v>
+        <v>19</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10462,19 +10261,19 @@
         <v>19</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>192</v>
+        <v>395</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10500,11 +10299,13 @@
         <v>19</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="Y74" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z74" t="s" s="2">
-        <v>425</v>
+        <v>19</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>19</v>
@@ -10522,7 +10323,7 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10537,35 +10338,35 @@
         <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>426</v>
+        <v>19</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>427</v>
+        <v>399</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>428</v>
+        <v>19</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>429</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>421</v>
+        <v>19</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>19</v>
@@ -10574,19 +10375,19 @@
         <v>19</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>431</v>
+        <v>174</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>432</v>
+        <v>401</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10636,13 +10437,13 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>19</v>
@@ -10651,24 +10452,24 @@
         <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>426</v>
+        <v>19</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>427</v>
+        <v>404</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>428</v>
+        <v>19</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>429</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10679,7 +10480,7 @@
         <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>19</v>
@@ -10688,20 +10489,18 @@
         <v>19</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>434</v>
+        <v>181</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>436</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>19</v>
@@ -10750,25 +10549,25 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>433</v>
+        <v>183</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>437</v>
+        <v>178</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>19</v>
@@ -10779,21 +10578,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>438</v>
+        <v>406</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>438</v>
+        <v>406</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>19</v>
@@ -10805,15 +10604,17 @@
         <v>19</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>168</v>
+        <v>131</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>19</v>
@@ -10862,25 +10663,25 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>19</v>
@@ -10891,14 +10692,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>439</v>
+        <v>407</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10911,24 +10712,26 @@
         <v>19</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>131</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="O78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>19</v>
       </c>
@@ -10976,7 +10779,7 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10994,7 +10797,7 @@
         <v>19</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>19</v>
@@ -11005,46 +10808,42 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>440</v>
+        <v>408</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>440</v>
+        <v>408</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>258</v>
+        <v>409</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>19</v>
       </c>
@@ -11092,47 +10891,47 @@
         <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>260</v>
+        <v>408</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>19</v>
+        <v>411</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>442</v>
+        <v>19</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>86</v>
@@ -11144,20 +10943,18 @@
         <v>19</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>19</v>
@@ -11206,10 +11003,10 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>86</v>
@@ -11221,24 +11018,24 @@
         <v>98</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>446</v>
+        <v>19</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>428</v>
+        <v>19</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>448</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>449</v>
+        <v>417</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>449</v>
+        <v>417</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11261,13 +11058,13 @@
         <v>19</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>450</v>
+        <v>418</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>451</v>
+        <v>418</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11297,10 +11094,10 @@
         <v>110</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>452</v>
+        <v>419</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>453</v>
+        <v>420</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>19</v>
@@ -11318,7 +11115,7 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>449</v>
+        <v>417</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11336,21 +11133,21 @@
         <v>19</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>172</v>
+        <v>421</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>19</v>
+        <v>422</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>454</v>
+        <v>423</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>454</v>
+        <v>423</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11373,13 +11170,13 @@
         <v>19</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>455</v>
+        <v>226</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>456</v>
+        <v>424</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11406,13 +11203,13 @@
         <v>19</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>19</v>
+        <v>426</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>19</v>
@@ -11430,7 +11227,7 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>454</v>
+        <v>423</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11448,21 +11245,21 @@
         <v>19</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>458</v>
+        <v>178</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>19</v>
+        <v>428</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>459</v>
+        <v>429</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>459</v>
+        <v>429</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11485,18 +11282,20 @@
         <v>19</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>460</v>
+        <v>226</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>461</v>
+        <v>430</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>462</v>
+        <v>431</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>19</v>
       </c>
@@ -11520,13 +11319,13 @@
         <v>19</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>19</v>
+        <v>434</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>19</v>
+        <v>435</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>19</v>
@@ -11544,7 +11343,7 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>459</v>
+        <v>429</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11562,21 +11361,21 @@
         <v>19</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>464</v>
+        <v>436</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>19</v>
+        <v>437</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11587,7 +11386,7 @@
         <v>77</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>19</v>
@@ -11599,17 +11398,15 @@
         <v>19</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>466</v>
+        <v>439</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>19</v>
@@ -11634,13 +11431,13 @@
         <v>19</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>19</v>
+        <v>441</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>19</v>
+        <v>442</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>19</v>
@@ -11658,13 +11455,13 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>19</v>
@@ -11676,21 +11473,21 @@
         <v>19</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>19</v>
+        <v>444</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11701,7 +11498,7 @@
         <v>77</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>19</v>
@@ -11713,13 +11510,13 @@
         <v>19</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>168</v>
+        <v>226</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>169</v>
+        <v>446</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>170</v>
+        <v>447</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11746,13 +11543,13 @@
         <v>19</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>19</v>
+        <v>448</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>19</v>
+        <v>449</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>19</v>
@@ -11770,50 +11567,50 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>171</v>
+        <v>445</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>172</v>
+        <v>450</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>19</v>
+        <v>451</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>19</v>
@@ -11825,17 +11622,15 @@
         <v>19</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>131</v>
+        <v>453</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>175</v>
+        <v>454</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>19</v>
@@ -11884,75 +11679,71 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>178</v>
+        <v>452</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>172</v>
+        <v>456</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>19</v>
+        <v>457</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>257</v>
+        <v>19</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>131</v>
+        <v>226</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>258</v>
+        <v>459</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>19</v>
       </c>
@@ -11976,13 +11767,13 @@
         <v>19</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>19</v>
+        <v>230</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>19</v>
+        <v>462</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>19</v>
@@ -12000,39 +11791,39 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>260</v>
+        <v>458</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>129</v>
+        <v>463</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>19</v>
+        <v>464</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12040,13 +11831,13 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>19</v>
@@ -12055,15 +11846,17 @@
         <v>19</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>467</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>19</v>
@@ -12112,13 +11905,13 @@
         <v>19</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>19</v>
@@ -12130,21 +11923,21 @@
         <v>19</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>161</v>
+        <v>469</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>476</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12167,13 +11960,13 @@
         <v>19</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>478</v>
+        <v>180</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>479</v>
+        <v>181</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>480</v>
+        <v>182</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12224,7 +12017,7 @@
         <v>19</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>477</v>
+        <v>183</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12236,13 +12029,13 @@
         <v>19</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>481</v>
+        <v>178</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>19</v>
@@ -12253,21 +12046,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>19</v>
@@ -12279,15 +12072,17 @@
         <v>19</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>192</v>
+        <v>131</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>483</v>
+        <v>185</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>19</v>
@@ -12312,13 +12107,13 @@
         <v>19</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>484</v>
+        <v>19</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>485</v>
+        <v>19</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>19</v>
@@ -12336,71 +12131,75 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>482</v>
+        <v>187</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>486</v>
+        <v>178</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>487</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>192</v>
+        <v>131</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>489</v>
+        <v>190</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>19</v>
       </c>
@@ -12424,13 +12223,13 @@
         <v>19</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>295</v>
+        <v>19</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>491</v>
+        <v>19</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>492</v>
+        <v>19</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>19</v>
@@ -12448,39 +12247,39 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>488</v>
+        <v>192</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>493</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12488,10 +12287,10 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>19</v>
@@ -12503,20 +12302,16 @@
         <v>19</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>192</v>
+        <v>474</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>19</v>
       </c>
@@ -12540,13 +12335,13 @@
         <v>19</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>295</v>
+        <v>19</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>499</v>
+        <v>19</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>19</v>
@@ -12564,13 +12359,13 @@
         <v>19</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>19</v>
@@ -12579,24 +12374,24 @@
         <v>98</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>19</v>
+        <v>477</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>501</v>
+        <v>300</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>19</v>
+        <v>478</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>502</v>
+        <v>479</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12607,7 +12402,7 @@
         <v>77</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>19</v>
@@ -12619,15 +12414,17 @@
         <v>19</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>504</v>
+        <v>481</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>19</v>
@@ -12652,13 +12449,13 @@
         <v>19</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>507</v>
+        <v>485</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>19</v>
@@ -12676,13 +12473,13 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>19</v>
@@ -12694,21 +12491,21 @@
         <v>19</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>509</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12719,7 +12516,7 @@
         <v>77</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>19</v>
@@ -12731,15 +12528,17 @@
         <v>19</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>19</v>
@@ -12764,13 +12563,13 @@
         <v>19</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>514</v>
+        <v>492</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>19</v>
@@ -12788,13 +12587,13 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>19</v>
@@ -12806,21 +12605,21 @@
         <v>19</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>515</v>
+        <v>19</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>516</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12843,13 +12642,13 @@
         <v>19</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>518</v>
+        <v>199</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>519</v>
+        <v>494</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12900,7 +12699,7 @@
         <v>19</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -12918,21 +12717,21 @@
         <v>19</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>521</v>
+        <v>293</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>522</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>523</v>
+        <v>496</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>523</v>
+        <v>496</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12955,13 +12754,13 @@
         <v>19</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>192</v>
+        <v>497</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>524</v>
+        <v>498</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12988,13 +12787,13 @@
         <v>19</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>295</v>
+        <v>19</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>526</v>
+        <v>19</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>527</v>
+        <v>19</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>19</v>
@@ -13012,7 +12811,7 @@
         <v>19</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>523</v>
+        <v>496</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -13027,24 +12826,24 @@
         <v>98</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>19</v>
+        <v>299</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>529</v>
+        <v>501</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>530</v>
+        <v>502</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>530</v>
+        <v>502</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13052,13 +12851,13 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G97" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="G97" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="H97" t="s" s="2">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>19</v>
@@ -13067,16 +12866,16 @@
         <v>19</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>250</v>
+        <v>503</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>531</v>
+        <v>504</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>532</v>
+        <v>505</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>533</v>
+        <v>506</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13126,13 +12925,13 @@
         <v>19</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>530</v>
+        <v>502</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>19</v>
@@ -13141,1040 +12940,20 @@
         <v>98</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>19</v>
+        <v>507</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>534</v>
+        <v>508</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
-      <c r="P98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
-      <c r="P101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O103" s="2"/>
-      <c r="P103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O106" s="2"/>
-      <c r="P106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AN106" t="s" s="2">
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN106">
+  <autoFilter ref="A1:AN97">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14184,7 +12963,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI105">
+  <conditionalFormatting sqref="A2:AI96">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-chul-encounter.xlsx
+++ b/StructureDefinition-chul-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-10T16:13:27+02:00</t>
+    <t>2025-09-12T12:04:03+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-chul-encounter.xlsx
+++ b/StructureDefinition-chul-encounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-12T12:04:03+02:00</t>
+    <t>2025-09-12T14:17:00+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1501,7 +1501,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.eu/fhir/base/StructureDefinition/location-eu)
+    <t xml:space="preserve">Reference(https://terminology.chuliege.be/fhir/StructureDefinition/chul-location)
 </t>
   </si>
   <si>

--- a/StructureDefinition-chul-encounter.xlsx
+++ b/StructureDefinition-chul-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-12T14:17:00+02:00</t>
+    <t>2026-02-04T18:27:09+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
